--- a/Docs/Test-Case/RTM.xlsx
+++ b/Docs/Test-Case/RTM.xlsx
@@ -1,43 +1,402 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="34">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,26 +404,398 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -111,7 +842,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -146,7 +877,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -320,20 +1051,829 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tên chức năng</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cấp độ ưu tiên</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Có UI không?</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID (Authorization)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID (FE - chờ Test_Case_FE.xlsx)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tình trạng Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Đăng ký tài khoản</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_REG_01 → 06</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_LOG_01, 02, 03</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Đăng xuất</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_LOG_04</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>[Phi chức năng] Đảm bảo role mặc định CUSTOMER khi đăng ký (hiện đang VI PHẠM - xem Bug đã log)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Authentication (Security)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Có (API)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-01</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROF-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Xem thông tin cá nhân</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-20</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>❌ CHƯA CÓ TEST CASE FE</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROF-02</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật thông tin cá nhân</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-21, TC-AUTH-22, TC-AUTH-23</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>❌ CHƯA CÓ TEST CASE FE</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Xem danh sách sản phẩm</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>❌ CHƯA CÓ TEST CASE FE (Customer xem danh sách SP)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-02</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Xem chi tiết sản phẩm</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>❌ CHƯA CÓ TEST CASE FE (Customer xem chi tiết SP)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-03</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Xem sản phẩm theo danh mục (Category)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>❌ CHƯA CÓ TEST CASE FE (Xem theo danh mục)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-04</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Thêm sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Không (API-only)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-02, TC-AUTH-03, TC-AUTH-04, TC-AUTH-26</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_NEG_01 (xác nhận không có UI)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Sửa sản phẩm</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-05, TC-AUTH-06, TC-AUTH-24, TC-AUTH-25</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_EMP_01→05, TC_FE_MGR_01→05</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROD-06</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Xóa sản phẩm</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; Category</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-07, TC-AUTH-08, TC-AUTH-09, TC-AUTH-27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_MGR_11, TC_FE_MGR_12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Thêm sản phẩm vào giỏ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-11, TC-AUTH-12, TC-AUTH-28</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CART_01, 02, 03</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-02</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật số lượng trong giỏ</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CART_04</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-03</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Xóa sản phẩm khỏi giỏ</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CART_05</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-04</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Gộp giỏ hàng local (merge)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Có (chạy ngầm)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CART_06</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-05</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Checkout (đặt hàng)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-10, TC-AUTH-13</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CHK_01, 02, 03</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ORD-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Xem danh sách đơn hàng</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-14, TC-AUTH-19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CHK_04, TC_FE_EMP_06, TC_FE_MRG_06</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ORD-02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Xem chi tiết đơn hàng</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-15</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_EMP_07, TC_FE_MRG_07 (⚠️ Customer chưa có case xem chi tiết đơn riêng)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ORD-03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Hủy đơn hàng</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-16</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_CUS_CHK_05</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ORD-04</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Xác nhận hoàn tất đơn hàng</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-17, TC-AUTH-18, TC-AUTH-29, TC-AUTH-30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>TC_FE_EMP_08,09,10, TC_FE_MRG_08,09,10</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Docs/Test-Case/RTM.xlsx
+++ b/Docs/Test-Case/RTM.xlsx
@@ -1526,9 +1526,9 @@
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Có</t>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Không (API-only)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1536,9 +1536,9 @@
           <t>TC-AUTH-07, TC-AUTH-08, TC-AUTH-09, TC-AUTH-27</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>TC_FE_MGR_11, TC_FE_MGR_12</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>TC-AUTH-07,08,09,27, TC_FE_NEG_02 (xác nhận không có UI)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
